--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N174_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N174_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>81.12288638023537</v>
+        <v>13.18246903678825</v>
       </c>
       <c r="D2" t="n">
-        <v>48.44068537913146</v>
+        <v>7.871611374108863</v>
       </c>
       <c r="E2" t="n">
-        <v>12.11617849240443</v>
+        <v>1.968879005015719</v>
       </c>
       <c r="F2" t="n">
-        <v>14.92671569816655</v>
+        <v>2.425591300952065</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>69.64397238669051</v>
+        <v>11.31714551283721</v>
       </c>
       <c r="D3" t="n">
-        <v>58.23658709939592</v>
+        <v>9.463445403651837</v>
       </c>
       <c r="E3" t="n">
-        <v>12.11617849240443</v>
+        <v>1.968879005015719</v>
       </c>
       <c r="F3" t="n">
-        <v>14.92671569816655</v>
+        <v>2.425591300952065</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.68144811995427</v>
+        <v>8.398235319492569</v>
       </c>
       <c r="D4" t="n">
-        <v>22.8318989666922</v>
+        <v>3.710183582087482</v>
       </c>
       <c r="E4" t="n">
-        <v>12.11617849240443</v>
+        <v>1.968879005015719</v>
       </c>
       <c r="F4" t="n">
-        <v>14.92671569816655</v>
+        <v>2.425591300952065</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
